--- a/Publications/GenAI/2_research_category/PB_v6/PB_v6_claude-sonnet-4-6_results_only-v5-incorrect.xlsx
+++ b/Publications/GenAI/2_research_category/PB_v6/PB_v6_claude-sonnet-4-6_results_only-v5-incorrect.xlsx
@@ -254,23 +254,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -530,159 +530,159 @@
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="2" t="b">
+      <c r="I2" s="3" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J2" s="2" t="b">
+      <c r="J2" s="3" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="56" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="2" t="b">
+      <c r="I3" s="3" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="b">
+      <c r="J3" s="3" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="56" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="2" t="b">
+      <c r="I4" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="b">
+      <c r="J4" s="3" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="L4" s="0" t="s">
+      <c r="L4" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L5" s="0" t="s">
+      <c r="L5" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L8" s="0" t="s">
+      <c r="L8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -706,62 +706,62 @@
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -785,35 +785,35 @@
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>3</v>
       </c>
     </row>
